--- a/data/kz/08_niche_formats.xlsx
+++ b/data/kz/08_niche_formats.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Форматы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Форматы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,43 +429,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ZEREK — Форматы ниш (fallback catalog).</t>
+          <t>ZEREK — Форматы ниш (v1.0 spec)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Используется Quick Check v2 когда в per-niche xlsx нет форматов.</t>
+          <t>format_type ∈ SOLO|HOME|MOBILE|KIOSK|HIGHWAY|PRODUCTION|STANDARD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ниш с форматами: 58</t>
+          <t>allowed_locations: CSV из config/locations.yaml или 'auto' (скрыт)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>class: эконом / стандарт / премиум ('' если без градации).</t>
+          <t>typical_staff: формат 'роль:n|роль2:m' или пусто для SOLO</t>
         </is>
       </c>
     </row>
@@ -492,2824 +494,3608 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>loc_type</t>
+          <t>capex_standard</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>capex_standard</t>
+          <t>class</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>format_type</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>allowed_locations</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>typical_staff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAKERY</t>
+          <t>BARBER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BAKERY_SMALL</t>
+          <t>BARBER_SOLO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Мини-пекарня с витриной</t>
+          <t>Барбер-одиночка</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>12000000</v>
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>эконом</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BAKERY</t>
+          <t>BARBER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAKERY_FULL</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Пекарня-кафе</t>
+          <t>Барбершоп 3-5 кресел</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>22000000</v>
+        <v>45</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>city_center,residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>барбер:4|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BAKERY</t>
+          <t>BARBER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAKERY_PRODUCTION</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Производство + доставка B2B</t>
+          <t>Премиум барбершоп</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>32000000</v>
+        <v>80</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>city_center,mall_premium,bc_premium</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>барбер:5|администратор:1|бариста:1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CANTEEN</t>
+          <t>BEAUTY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CANTEEN_BC</t>
+          <t>BEAUTY_SOLO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Столовая в бизнес-центре</t>
+          <t>Мастер в чужом салоне</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>90</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>business_center</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>14000000</v>
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CANTEEN</t>
+          <t>BEAUTY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CANTEEN_ENTER</t>
+          <t>BEAUTY_STANDARD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Столовая при предприятии</t>
+          <t>Салон красоты</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>20000000</v>
+        <v>80</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>city_center,residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>парикмахер:2|мастер_маникюра:2|косметолог:1|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CATERING</t>
+          <t>BEAUTY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CATERING_HOME</t>
+          <t>BEAUTY_PREMIUM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Домашний кейтеринг</t>
+          <t>Премиум салон</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>3000000</v>
+        <v>120</v>
+      </c>
+      <c r="E12" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>city_center,mall_premium,bc_premium</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>парикмахер:3|мастер_маникюра:2|косметолог:2|администратор:2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CATERING</t>
+          <t>MANICURE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CATERING_STUDIO</t>
+          <t>NAIL_HOME</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Студия-цех</t>
+          <t>Мастер на дому</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>15000000</v>
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>350000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CATERING</t>
+          <t>MANICURE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CATERING_EVENT</t>
+          <t>NAIL_SOLO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Крупный event-кейтеринг</t>
+          <t>Мастер в чужом салоне</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>150</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>40000000</v>
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COFFEE</t>
+          <t>MANICURE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COFFEE_KIOSK</t>
+          <t>NAIL_CABINET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Островок / кофе с собой</t>
+          <t>Кабинет 1-2 мастера</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>6000000</v>
+        <v>20</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>мастер_маникюра:2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COFFEE</t>
+          <t>MANICURE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COFFEE_CAFE</t>
+          <t>NAIL_SALON</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Кофейня-кафе</t>
+          <t>Студия маникюра</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>18000000</v>
+        <v>50</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>city_center,mall_premium,mall_standard</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>мастер_маникюра:4|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COFFEE</t>
+          <t>BROW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COFFEE_SPECIAL</t>
+          <t>BROW_HOME</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Specialty coffee</t>
+          <t>Мастер на дому</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>32000000</v>
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CONFECTION</t>
+          <t>BROW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CONFECT_HOME</t>
+          <t>BROW_SOLO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Домашний кондитер</t>
+          <t>Мастер в чужом салоне</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1500000</v>
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>эконом</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CONFECTION</t>
+          <t>BROW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CONFECT_WORKSHOP</t>
+          <t>BROW_CABINET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Кондитерский цех</t>
+          <t>Свой кабинет</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>12000000</v>
+        <v>18</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>мастер:2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DONER</t>
+          <t>LASH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DONER_TAKEOUT</t>
+          <t>LASH_HOME</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Донерная навынос</t>
+          <t>Мастер на дому</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>5500000</v>
+        <v>8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>эконом</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DONER</t>
+          <t>LASH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DONER_CAFE</t>
+          <t>LASH_SOLO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Донерная с залом</t>
+          <t>Мастер в чужом салоне</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>14000000</v>
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FASTFOOD</t>
+          <t>LASH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FASTFOOD_TAKE</t>
+          <t>LASH_CABINET</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Формат take-away</t>
+          <t>Свой кабинет</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>7000000</v>
+        <v>18</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>мастер:2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FASTFOOD</t>
+          <t>SUGARING</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FASTFOOD_CAFE</t>
+          <t>SUGAR_HOME</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Фастфуд с залом</t>
+          <t>Мастер на дому</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>18000000</v>
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>350000</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PIZZA</t>
+          <t>SUGARING</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PIZZA_DELIVERY</t>
+          <t>SUGAR_SOLO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Доставка пиццы</t>
+          <t>Мастер в чужом салоне</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>9000000</v>
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>эконом</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PIZZA</t>
+          <t>SUGARING</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PIZZA_CAFE</t>
+          <t>SUGAR_CABINET</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Пиццерия с залом</t>
+          <t>Кабинет шугаринга</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>22000000</v>
+        <v>20</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>мастер:2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SUSHI</t>
+          <t>MASSAGE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SUSHI_DELIVERY</t>
+          <t>MASSAGE_HOME</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Доставка суши</t>
+          <t>Выезд на дом</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>9000000</v>
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>эконом</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUSHI</t>
+          <t>MASSAGE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SUSHI_BAR</t>
+          <t>MASSAGE_SOLO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Суши-бар с залом</t>
+          <t>Мастер в чужом салоне</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>26000000</v>
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BUBBLETEA</t>
+          <t>MASSAGE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BUBBLE_KIOSK</t>
+          <t>MASSAGE_STUDIO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Островок в ТЦ</t>
+          <t>Массажная студия</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>4500000</v>
+        <v>40</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>массажист:2|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BUBBLETEA</t>
+          <t>COSMETOLOGY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BUBBLE_CAFE</t>
+          <t>COSM_SOLO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Бабл-ти с залом</t>
+          <t>Косметолог в чужом салоне</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>12000000</v>
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MEATSHOP</t>
+          <t>COSMETOLOGY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEAT_SMALL</t>
+          <t>COSM_CABINET</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Небольшая лавка</t>
+          <t>Кабинет косметолога</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>25</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>5500000</v>
+      <c r="E30" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard,bc_standard</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>косметолог:1|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MEATSHOP</t>
+          <t>COSMETOLOGY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MEAT_STANDARD</t>
+          <t>COSM_CLINIC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Полноценная мясная лавка</t>
+          <t>Мини-клиника</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>12000000</v>
+        <v>60</v>
+      </c>
+      <c r="E31" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>city_center,mall_premium,bc_premium</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>косметолог:2|врач:1|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FRUITSVEGS</t>
+          <t>DENTAL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FV_KIOSK</t>
+          <t>DENTAL_1CH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Киоск</t>
+          <t>Кабинет 1 кресло</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>2500000</v>
+        <v>30</v>
+      </c>
+      <c r="E32" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,bc_standard</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>стоматолог:1|ассистент:1|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FRUITSVEGS</t>
+          <t>DENTAL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FV_STORE</t>
+          <t>DENTAL_CLINIC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Овощной магазин</t>
+          <t>Клиника 3-5 кресел</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>40</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>7000000</v>
+        <v>80</v>
+      </c>
+      <c r="E33" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>city_center,residential,mall_standard</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>стоматолог:3|ассистент:3|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEMIFOOD</t>
+          <t>OPTICS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SEMI_HOME</t>
+          <t>OPTICS_TC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Домашнее производство</t>
+          <t>Оптика в ТЦ</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>2500000</v>
+        <v>40</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>mall_premium,mall_standard</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>продавец:2|офтальмолог:1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEMIFOOD</t>
+          <t>OPTICS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SEMI_WORKSHOP</t>
+          <t>OPTICS_STREET</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Мини-цех</t>
+          <t>Оптика-улица</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>70</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>14000000</v>
+      <c r="E35" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>city_center,residential,residential_complex</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>продавец:2|офтальмолог:1|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WATERPLANT</t>
+          <t>TAILOR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WATER_MINI</t>
+          <t>TAILOR_HOME</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Мини-линия розлива</t>
+          <t>Ателье на дому</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>100</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>18000000</v>
+        <v>15</v>
+      </c>
+      <c r="E36" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WATERPLANT</t>
+          <t>TAILOR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WATER_FULL</t>
+          <t>TAILOR_MINI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Завод розлива</t>
+          <t>Мини-ателье</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>300</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>55000000</v>
+        <v>25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard,market</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>закройщик:1|швея:1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PETSHOP</t>
+          <t>REPAIR_PHONE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PET_SMALL</t>
+          <t>REPAIR_POINT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Зоомагазин мини</t>
+          <t>Точка в ТЦ</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>30</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>5000000</v>
+        <v>12</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>KIOSK</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>mall_premium,mall_standard,bc_standard</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>мастер:1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PETSHOP</t>
+          <t>REPAIR_PHONE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PET_FULL</t>
+          <t>REPAIR_STUDIO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Полноценный зоомагазин</t>
+          <t>Мастерская</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>80</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>14000000</v>
+        <v>25</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>city_center,residential,mall_standard</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>мастер:2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BARBER</t>
+          <t>PHOTO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BARBER_SOLO</t>
+          <t>PHOTO_HOME</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Барбер на одно кресло</t>
+          <t>Выездной фотограф</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1800000</v>
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>эконом</t>
-        </is>
-      </c>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BARBER</t>
+          <t>PHOTO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BARBER_STANDARD</t>
+          <t>PHOTO_STUDIO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Барбершоп 3-5 кресел</t>
+          <t>Фотостудия с интерьерами</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>45</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>7500000</v>
+        <v>60</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>city_center,residential_complex,bc_standard,industrial</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>фотограф:1|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BARBER</t>
+          <t>DETAILING</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BARBER_PREMIUM</t>
+          <t>DETAIL_BOX1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Премиум барбершоп</t>
+          <t>Одиночный бокс</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>80</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>18000000</v>
+      <c r="E42" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>HIGHWAY</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>детейлер:2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BEAUTY</t>
+          <t>DETAILING</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BEAUTY_MINI</t>
+          <t>DETAIL_STUDIO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Салон на 3 кресла</t>
+          <t>Детейлинг-студия</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>40</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>6000000</v>
+        <v>150</v>
+      </c>
+      <c r="E43" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>city_center,industrial,highway</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>детейлер:3|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BEAUTY</t>
+          <t>NOTARY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BEAUTY_STANDARD</t>
+          <t>NOTARY_OFFICE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Полноценный салон</t>
+          <t>Нотариальная контора</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>80</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>16000000</v>
+        <v>30</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>city_center,bc_premium,bc_standard</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>нотариус:1|помощник:1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BEAUTY</t>
+          <t>COFFEE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BEAUTY_PREMIUM</t>
+          <t>COFFEE_KIOSK</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Премиум салон</t>
+          <t>Островок / кофе с собой</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>120</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>32000000</v>
+        <v>12</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>KIOSK</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>mall_premium,mall_standard,bc_premium,bc_standard</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>бариста:2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MANICURE</t>
+          <t>COFFEE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>COFFEE_CAFE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>На дому</t>
+          <t>Кофейня-кафе</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>350000</v>
+        <v>60</v>
+      </c>
+      <c r="E46" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>city_center,residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>бариста:3|кассир:1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MANICURE</t>
+          <t>COFFEE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>COFFEE_SPECIAL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Кабинет 1-2 мастера</t>
+          <t>Specialty coffee</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>2200000</v>
+        <v>80</v>
+      </c>
+      <c r="E47" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>city_center,mall_premium,bc_premium</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>бариста:3|кассир:1|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MANICURE</t>
+          <t>BAKERY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NAIL_SALON</t>
+          <t>BAKERY_SMALL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Студия маникюра</t>
+          <t>Мини-пекарня с витриной</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>50</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>9000000</v>
+        <v>45</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,market</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>пекарь:2|продавец:1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BROW</t>
+          <t>BAKERY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BROW_HOME</t>
+          <t>BAKERY_FULL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>На дому</t>
+          <t>Пекарня-кафе</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>300000</v>
+        <v>80</v>
+      </c>
+      <c r="E49" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>city_center,residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>пекарь:3|продавец:2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BROW</t>
+          <t>BAKERY</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BAKERY_PRODUCTION</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Свой кабинет</t>
+          <t>Производство + B2B</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>18</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>2000000</v>
+        <v>120</v>
+      </c>
+      <c r="E50" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>пекарь:4|менеджер_b2b:1|водитель:1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LASH</t>
+          <t>CONFECTION</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LASH_HOME</t>
+          <t>CONFECT_HOME</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>На дому</t>
+          <t>Домашний кондитер</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>300000</v>
+        <v>20</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>эконом</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LASH</t>
+          <t>CONFECTION</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>CONFECT_WORKSHOP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Свой кабинет</t>
+          <t>Кондитерский цех</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>18</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>2000000</v>
+        <v>60</v>
+      </c>
+      <c r="E52" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,industrial</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>кондитер:3|помощник:1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SUGARING</t>
+          <t>DONER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SUGAR_HOME</t>
+          <t>DONER_TAKEOUT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>На дому</t>
+          <t>Донерная навынос</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>350000</v>
+        <v>18</v>
+      </c>
+      <c r="E53" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,market</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>повар:2|кассир:1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SUGARING</t>
+          <t>DONER</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SUGAR_CABINET</t>
+          <t>DONER_CAFE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Кабинет шугаринга</t>
+          <t>Донерная с залом</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>20</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>2500000</v>
+        <v>55</v>
+      </c>
+      <c r="E54" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>city_center,residential,mall_standard</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>повар:3|кассир:1|официант:1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MASSAGE</t>
+          <t>FASTFOOD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MASSAGE_HOME</t>
+          <t>FASTFOOD_TAKE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Выезд на дом</t>
+          <t>Такаут в ТЦ</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>300000</v>
+        <v>25</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>KIOSK</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>mall_premium,mall_standard,bc_standard</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>повар:2|кассир:1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MASSAGE</t>
+          <t>FASTFOOD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MASSAGE_STUDIO</t>
+          <t>FASTFOOD_CAFE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Массажная студия</t>
+          <t>Фастфуд с залом</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>40</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>7000000</v>
+        <v>70</v>
+      </c>
+      <c r="E56" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>city_center,residential,mall_standard</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>повар:3|кассир:2|официант:1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>COSMETOLOGY</t>
+          <t>PIZZA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COSM_CABINET</t>
+          <t>PIZZA_DELIVERY</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Кабинет косметолога</t>
+          <t>Доставка пиццы</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>25</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>6000000</v>
+        <v>30</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>пиццмейкер:2|курьер:2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>COSMETOLOGY</t>
+          <t>PIZZA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>COSM_CLINIC</t>
+          <t>PIZZA_CAFE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Мини-клиника</t>
+          <t>Пиццерия с залом</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
+        <v>80</v>
+      </c>
+      <c r="E58" t="n">
         <v>22000000</v>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>city_center,residential,mall_standard</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>пиццмейкер:3|кассир:1|официант:2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DENTAL</t>
+          <t>SUSHI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DENTAL_1CH</t>
+          <t>SUSHI_DELIVERY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Кабинет на 1 кресло</t>
+          <t>Доставка суши</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>30</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>12000000</v>
+      <c r="E59" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>сушист:2|курьер:2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DENTAL</t>
+          <t>SUSHI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>SUSHI_BAR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Клиника на 3-5 кресел</t>
+          <t>Суши-бар с залом</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>80</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>45000000</v>
+        <v>75</v>
+      </c>
+      <c r="E60" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>city_center,residential,mall_standard</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>сушист:3|кассир:1|официант:2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PHARMACY</t>
+          <t>BUBBLETEA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PHARM_SMALL</t>
+          <t>BUBBLE_KIOSK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Небольшая аптека</t>
+          <t>Островок в ТЦ</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>40</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>residential_area</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>10000000</v>
+        <v>10</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>KIOSK</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>mall_premium,mall_standard,bc_premium,bc_standard</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>бариста:2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PHARMACY</t>
+          <t>BUBBLETEA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PHARM_FULL</t>
+          <t>BUBBLE_CAFE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Сетевая аптека</t>
+          <t>Бабл-ти с залом</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>22000000</v>
+        <v>40</v>
+      </c>
+      <c r="E62" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>city_center,mall_standard,residential_complex</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>бариста:3|кассир:1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OPTICS</t>
+          <t>CANTEEN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OPTICS_TC</t>
+          <t>CANTEEN_BC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Оптика в ТЦ</t>
+          <t>Столовая в БЦ</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>40</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>16000000</v>
+        <v>90</v>
+      </c>
+      <c r="E63" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>bc_standard,bc_premium</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>повар:3|кассир:2|помощник:2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OPTICS</t>
+          <t>CANTEEN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OPTICS_STREET</t>
+          <t>CANTEEN_ENTER</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Оптика-улица с залом</t>
+          <t>Столовая при предприятии</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>70</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>24000000</v>
+        <v>140</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>повар:4|кассир:2|помощник:2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FITNESS</t>
+          <t>SEMIFOOD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FIT_STUDIO</t>
+          <t>SEMI_HOME</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Студия 100 м²</t>
+          <t>Домашнее производство</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>100</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>residential_area</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>14000000</v>
+        <v>25</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>эконом</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FITNESS</t>
+          <t>SEMIFOOD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FIT_CLUB</t>
+          <t>SEMI_WORKSHOP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Фитнес-клуб 500 м²</t>
+          <t>Мини-цех</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>500</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>80000000</v>
+        <v>70</v>
+      </c>
+      <c r="E66" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>повар:3|помощник:2|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>YOGA</t>
+          <t>CATERING</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YOGA_STUDIO</t>
+          <t>CATERING_HOME</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Йога-студия</t>
+          <t>Домашний кейтеринг</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>80</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>residential_complex</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>6000000</v>
+        <v>35</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HOTEL</t>
+          <t>CATERING</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HOTEL_HOSTEL</t>
+          <t>CATERING_STUDIO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Хостел 20 койко-мест</t>
+          <t>Студия-цех</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>150</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>18000000</v>
+        <v>80</v>
+      </c>
+      <c r="E68" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>повар:3|помощник:2|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HOTEL</t>
+          <t>CATERING</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HOTEL_3STAR</t>
+          <t>CATERING_EVENT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Мини-отель 2-3★</t>
+          <t>Event-кейтеринг</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>400</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>90000000</v>
+        <v>150</v>
+      </c>
+      <c r="E69" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>повар:5|помощник:4|менеджер:2|логист:1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HOTEL</t>
+          <t>MEATSHOP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HOTEL_4STAR</t>
+          <t>MEAT_SMALL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Отель 4-5★</t>
+          <t>Небольшая лавка</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>320000000</v>
+        <v>25</v>
+      </c>
+      <c r="E70" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>residential,market,residential_complex</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>продавец:1|разделщик:1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AUTOSERVICE</t>
+          <t>MEATSHOP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AUTOSERV_1POST</t>
+          <t>MEAT_STANDARD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Автосервис 1-2 поста</t>
+          <t>Мясная лавка</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>80</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>highway</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>5000000</v>
+        <v>50</v>
+      </c>
+      <c r="E71" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,market</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>продавец:2|разделщик:1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AUTOSERVICE</t>
+          <t>FRUITSVEGS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AUTOSERV_FULL</t>
+          <t>FV_KIOSK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>СТО 3-6 постов</t>
+          <t>Киоск</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>200</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>highway</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>20000000</v>
+        <v>10</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>market,residential,residential_complex</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>продавец:1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TIRESERVICE</t>
+          <t>FRUITSVEGS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TIRE_SMALL</t>
+          <t>FV_STORE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Шиномонтаж 1 пост</t>
+          <t>Магазин</t>
         </is>
       </c>
       <c r="D73" t="n">
         <v>40</v>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>highway</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>3000000</v>
+      <c r="E73" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,market</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>продавец:2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TIRESERVICE</t>
+          <t>FLOWERS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TIRE_STANDARD</t>
+          <t>FLOWER_KIOSK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Шиномонтаж 2-3 поста</t>
+          <t>Цветочный киоск</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>80</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>highway</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>8000000</v>
+        <v>12</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>city_center,residential,market,residential_complex</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>флорист:1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CARWASH</t>
+          <t>FLOWERS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WASH_SELF</t>
+          <t>FLOWER_STUDIO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Самомойка</t>
+          <t>Цветочная студия</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>250</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>highway</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>28000000</v>
+        <v>40</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>city_center,residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>флорист:2|курьер:1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CARWASH</t>
+          <t>AUTOPARTS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WASH_MANUAL</t>
+          <t>PARTS_STORE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ручная мойка 2-3 поста</t>
+          <t>Магазин автозапчастей</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>120</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>highway</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>14000000</v>
+        <v>80</v>
+      </c>
+      <c r="E76" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>residential,market,industrial,highway</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>продавец:2|консультант:1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CARWASH</t>
+          <t>BUILDMAT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WASH_PREMIUM</t>
+          <t>BUILD_SMALL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Премиум автомойка</t>
+          <t>Небольшой магазин</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>160</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>32000000</v>
+        <v>80</v>
+      </c>
+      <c r="E77" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>residential,industrial,market</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>продавец:2|водитель:1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DETAILING</t>
+          <t>BUILDMAT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DETAIL_BOX1</t>
+          <t>BUILD_FULL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Одиночный бокс</t>
+          <t>Строймаркет</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>highway</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>6500000</v>
+        <v>250</v>
+      </c>
+      <c r="E78" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>industrial,highway,suburb</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>продавец:3|водитель:2|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DETAILING</t>
+          <t>PETSHOP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DETAIL_STUDIO</t>
+          <t>PET_SMALL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Детейлинг-студия</t>
+          <t>Зоомагазин мини</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>150</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>22000000</v>
+        <v>30</v>
+      </c>
+      <c r="E79" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,market</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>продавец:1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AUTOPARTS</t>
+          <t>PETSHOP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PARTS_STORE</t>
+          <t>PET_FULL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Магазин автозапчастей</t>
+          <t>Зоомагазин</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>80</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>12000000</v>
+      <c r="E80" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>residential,mall_standard,residential_complex</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>продавец:2|грумер:1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CLEAN_SOLO</t>
+          <t>PHARM_SMALL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Клининг-ИП</t>
+          <t>Небольшая аптека</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>500000</v>
+        <v>40</v>
+      </c>
+      <c r="E81" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,suburb</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>фармацевт:2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CLEAN_TEAM</t>
+          <t>PHARM_FULL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Клининговая бригада</t>
+          <t>Сетевая аптека</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>60</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>business_center</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>4000000</v>
+        <v>80</v>
+      </c>
+      <c r="E82" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>city_center,residential,mall_standard</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>фармацевт:3|кассир:1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CARPETCLEAN</t>
+          <t>GROCERY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CARPET_WORKSHOP</t>
+          <t>GROC_KIOSK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Цех чистки ковров</t>
+          <t>Минимаркет</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>120</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>10000000</v>
+        <v>25</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,suburb</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>продавец:2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DRYCLEAN</t>
+          <t>GROCERY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DRY_APPR</t>
+          <t>GROC_STANDARD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Приёмка / пункт</t>
+          <t>Минимаркет</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>20</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>residential_complex</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>2500000</v>
+        <v>80</v>
+      </c>
+      <c r="E84" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,market</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>продавец:3|кассир:1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DRYCLEAN</t>
+          <t>GROCERY</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DRY_FULL</t>
+          <t>GROC_SUPER</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Химчистка с оборудованием</t>
+          <t>Супермаркет</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>80</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>18000000</v>
+        <v>250</v>
+      </c>
+      <c r="E85" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>city_center,residential,mall_standard</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>продавец:5|кассир:3|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LAUNDRY</t>
+          <t>WATERPLANT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LAUNDRY_SELF</t>
+          <t>WATER_MINI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Прачечная самообслуживания</t>
+          <t>Мини-линия розлива</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>60</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>residential_complex</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>14000000</v>
+        <v>100</v>
+      </c>
+      <c r="E86" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>оператор:2|водитель:1|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LAUNDRY</t>
+          <t>WATERPLANT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LAUNDRY_FULL</t>
+          <t>WATER_FULL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Промышленная прачечная</t>
+          <t>Завод розлива</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>200</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>42000000</v>
+        <v>300</v>
+      </c>
+      <c r="E87" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>оператор:4|водитель:2|менеджер:1|логист:1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KINDERGARTEN</t>
+          <t>FITNESS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KG_HOME</t>
+          <t>FIT_STUDIO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Домашний сад 8-12 детей</t>
+          <t>Студия 100 м²</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>70</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>residential_area</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>2500000</v>
+        <v>100</v>
+      </c>
+      <c r="E88" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>тренер:2|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KINDERGARTEN</t>
+          <t>FITNESS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KG_STANDARD</t>
+          <t>FIT_CLUB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Частный сад 30+ детей</t>
+          <t>Фитнес-клуб 500 м²</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>200</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>18000000</v>
+        <v>500</v>
+      </c>
+      <c r="E89" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>тренер:5|администратор:3|уборщик:2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KIDSCENTER</t>
+          <t>YOGA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KIDS_STUDIO</t>
+          <t>YOGA_STUDIO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Развивающая студия</t>
+          <t>Йога-студия</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>80</v>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>residential_area</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>5000000</v>
+      <c r="E90" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>residential_complex,city_center,mall_standard</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>тренер:2|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KIDSCENTER</t>
+          <t>LANGUAGES</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KIDS_LARGE</t>
+          <t>LANG_HOME</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Центр с несколькими программами</t>
+          <t>Репетитор из дома</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>200</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>16000000</v>
+        <v>15</v>
+      </c>
+      <c r="E91" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3319,28 +4105,38 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LANG_HOME</t>
+          <t>LANG_MICRO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Репетиторство из дома</t>
+          <t>Мини-школа</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>15</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>400000</v>
+        <v>60</v>
+      </c>
+      <c r="E92" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,bc_standard</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>преподаватель:3|администратор:1</t>
         </is>
       </c>
     </row>
@@ -3352,1216 +4148,1820 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LANG_MICRO</t>
+          <t>LANG_FULL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Мини-школа на 2-3 аудитории</t>
+          <t>Языковая школа</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>60</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>business_center</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>3500000</v>
+        <v>150</v>
+      </c>
+      <c r="E93" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>city_center,mall_standard,bc_standard</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>преподаватель:5|администратор:1|методист:1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LANGUAGES</t>
+          <t>KIDSCENTER</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LANG_FULL</t>
+          <t>KIDS_STUDIO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Языковая школа</t>
+          <t>Развивающая студия</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>150</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>14000000</v>
+        <v>80</v>
+      </c>
+      <c r="E94" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>педагог:3|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DRIVING</t>
+          <t>KIDSCENTER</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DRIVE_SMALL</t>
+          <t>KIDS_LARGE</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Автошкола 2-3 машины</t>
+          <t>Центр с несколькими программами</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>50</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>12000000</v>
+        <v>200</v>
+      </c>
+      <c r="E95" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>city_center,residential,mall_standard</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>педагог:5|администратор:1|методист:1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DRIVING</t>
+          <t>KINDERGARTEN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DRIVE_FULL</t>
+          <t>KG_HOME</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Автошкола 8+ машин</t>
+          <t>Домашний сад 8-12 детей</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>120</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>32000000</v>
+        <v>70</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>KINDERGARTEN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CARGO_SOLO</t>
+          <t>KG_STANDARD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1 машина</t>
+          <t>Частный сад 30+ детей</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>8000000</v>
+        <v>200</v>
+      </c>
+      <c r="E97" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>воспитатель:4|повар:1|медсестра:1|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>ACCOUNTING</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CARGO_FLEET</t>
+          <t>ACC_SOLO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Парк 5+ машин</t>
+          <t>Самозанятый бухгалтер</t>
         </is>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>45000000</v>
+      <c r="E98" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PVZ</t>
+          <t>ACCOUNTING</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>ACC_AGENCY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ПВЗ 15 м²</t>
+          <t>Бухгалтерское агентство</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>15</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>2500000</v>
+        <v>40</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>bc_standard,bc_premium,city_center</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>бухгалтер:3|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PVZ</t>
+          <t>CROSSFIT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PVZ_FULL</t>
+          <t>CROSSFIT_STUDIO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ПВЗ 35 м²</t>
+          <t>Кроссфит-зал</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>35</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>residential_complex</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>4500000</v>
+        <v>200</v>
+      </c>
+      <c r="E100" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>тренер:3|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>REPAIR_PHONE</t>
+          <t>MARTIAL_ARTS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>REPAIR_POINT</t>
+          <t>MMA_STUDIO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Точка ремонта</t>
+          <t>Зал единоборств</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>1800000</v>
+        <v>150</v>
+      </c>
+      <c r="E101" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>residential,industrial,mall_standard</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>тренер:3|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>REPAIR_PHONE</t>
+          <t>FOOTBALL_SCHOOL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>REPAIR_STUDIO</t>
+          <t>FB_SMALL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Мастерская</t>
+          <t>Детская футбольная школа</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>25</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>4500000</v>
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>тренер:3|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TAILOR</t>
+          <t>GROUP_FITNESS</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TAILOR_HOME</t>
+          <t>GF_STUDIO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ателье на дому</t>
+          <t>Студия групповых</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>15</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>500000</v>
+        <v>100</v>
+      </c>
+      <c r="E103" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>residential_complex,mall_standard,city_center</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>тренер:3|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TAILOR</t>
+          <t>REALTOR</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TAILOR_MINI</t>
+          <t>REAL_SOLO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Мини-ателье</t>
+          <t>Независимый риэлтор</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>25</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>2500000</v>
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TAILOR</t>
+          <t>REALTOR</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TAILOR_FULL</t>
+          <t>REAL_AGENCY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Полное ателье</t>
+          <t>Агентство недвижимости</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>60</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>9000000</v>
+        <v>50</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>bc_standard,bc_premium,city_center</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>риэлтор:3|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PHOTO</t>
+          <t>EVALUATION</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PHOTO_HOME</t>
+          <t>EVAL_SOLO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Выездной фотограф</t>
+          <t>Оценщик-самозанятый</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>1500000</v>
+      <c r="E106" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>эконом</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PHOTO</t>
+          <t>EVALUATION</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PHOTO_STUDIO</t>
+          <t>EVAL_AGENCY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Фотостудия с интерьерами</t>
+          <t>Оценочная компания</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>60</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>10000000</v>
+        <v>30</v>
+      </c>
+      <c r="E107" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>bc_standard,bc_premium,city_center</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>оценщик:2|помощник:1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FLOWERS</t>
+          <t>FURNITURE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FLOWER_KIOSK</t>
+          <t>FURN_SMALL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Цветочный киоск</t>
+          <t>Цех мебели на заказ</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>2500000</v>
+        <v>120</v>
+      </c>
+      <c r="E108" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>столяр:3|монтажник:1|дизайнер:1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FLOWERS</t>
+          <t>FURNITURE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FLOWER_STUDIO</t>
+          <t>FURN_FULL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Цветочная студия</t>
+          <t>Мебельное производство</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>40</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>8000000</v>
+        <v>300</v>
+      </c>
+      <c r="E109" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>столяр:5|монтажник:2|дизайнер:1|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PRINTING</t>
+          <t>LOFTFURNITURE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PRINT_SMALL</t>
+          <t>LOFT_SMALL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Мини-типография</t>
+          <t>Мастерская лофт-мебели</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>40</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>6500000</v>
+        <v>120</v>
+      </c>
+      <c r="E110" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>сварщик:2|столяр:1|монтажник:1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PRINTING</t>
+          <t>LOFTFURNITURE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PRINT_FULL</t>
+          <t>LOFT_FULL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Полноценная типография</t>
+          <t>Цех металлоконструкций</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>150</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>38000000</v>
+        <v>250</v>
+      </c>
+      <c r="E111" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>сварщик:3|столяр:1|монтажник:2|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GROCERY</t>
+          <t>PRINTING</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GROC_KIOSK</t>
+          <t>PRINT_SMALL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Киоск / минимаркет</t>
+          <t>Мини-типография</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>25</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>residential_area</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>3500000</v>
+        <v>40</v>
+      </c>
+      <c r="E112" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>city_center,industrial,bc_standard</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>оператор:2|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GROCERY</t>
+          <t>PRINTING</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GROC_STANDARD</t>
+          <t>PRINT_FULL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Минимаркет</t>
+          <t>Полноценная типография</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>80</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>residential_area</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>14000000</v>
+        <v>150</v>
+      </c>
+      <c r="E113" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>оператор:3|менеджер:1|дизайнер:1|водитель:1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GROCERY</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GROC_SUPER</t>
+          <t>CARGO_SOLO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Супермаркет</t>
+          <t>1 машина (InDrive)</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>250</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>48000000</v>
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BUILDMAT</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BUILD_SMALL</t>
+          <t>CARGO_FLEET</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Небольшой магазин</t>
+          <t>Парк 5+ машин</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>80</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>12000000</v>
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>водитель:5|диспетчер:1|механик:1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BUILDMAT</t>
+          <t>AUTOSERVICE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BUILD_FULL</t>
+          <t>AUTOSERV_1POST</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Полноценный строймаркет</t>
+          <t>Автосервис 1-2 поста</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>250</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>48000000</v>
+        <v>80</v>
+      </c>
+      <c r="E116" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>HIGHWAY</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>автослесарь:2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>COMPCLUB</t>
+          <t>AUTOSERVICE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CC_SMALL</t>
+          <t>AUTOSERV_FULL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Клуб 10-15 мест</t>
+          <t>СТО 3-6 постов</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>80</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>residential_area</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>18000000</v>
+        <v>200</v>
+      </c>
+      <c r="E117" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>HIGHWAY</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>автослесарь:4|приёмщик:1|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>COMPCLUB</t>
+          <t>TIRESERVICE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CC_LARGE</t>
+          <t>TIRE_SMALL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Киберарена 30+ мест</t>
+          <t>Шиномонтаж 1 пост</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>200</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>60000000</v>
+        <v>40</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>HIGHWAY</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>шиномонтажник:2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FURNITURE</t>
+          <t>TIRESERVICE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FURN_SMALL</t>
+          <t>TIRE_STANDARD</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Цех мебели на заказ</t>
+          <t>Шиномонтаж 2-3 поста</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>120</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>14000000</v>
+        <v>80</v>
+      </c>
+      <c r="E119" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>HIGHWAY</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>шиномонтажник:3|приёмщик:1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FURNITURE</t>
+          <t>CARWASH</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FURN_FULL</t>
+          <t>WASH_SELF</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Мебельное производство</t>
+          <t>Самомойка</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>300</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>42000000</v>
+        <v>250</v>
+      </c>
+      <c r="E120" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>премиум</t>
+          <t>HIGHWAY</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>оператор:1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LOFTFURNITURE</t>
+          <t>CARWASH</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LOFT_SMALL</t>
+          <t>WASH_MANUAL</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Мастерская лофт-мебели</t>
+          <t>Ручная мойка</t>
         </is>
       </c>
       <c r="D121" t="n">
         <v>120</v>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>12000000</v>
+      <c r="E121" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>HIGHWAY</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>мойщик:3|администратор:1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LOFTFURNITURE</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LOFT_FULL</t>
+          <t>CLEAN_SOLO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Цех металлоконструкций</t>
+          <t>Клининг-ИП</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>250</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>own_building</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>32000000</v>
+        <v>10</v>
+      </c>
+      <c r="E122" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>премиум</t>
-        </is>
-      </c>
+          <t>SOLO</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>rent_in_salon</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ACCOUNTING</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ACC_SOLO</t>
+          <t>CLEAN_TEAM</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Самозанятый бухгалтер</t>
+          <t>Клининговая бригада</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>250000</v>
+        <v>60</v>
+      </c>
+      <c r="E123" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>уборщик:4|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ACCOUNTING</t>
+          <t>CARPETCLEAN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ACC_AGENCY</t>
+          <t>CARPET_WORKSHOP</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Бухгалтерское агентство</t>
+          <t>Цех чистки ковров</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>40</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>business_center</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>3500000</v>
+        <v>120</v>
+      </c>
+      <c r="E124" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>оператор:2|водитель:1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>REALTOR</t>
+          <t>DRYCLEAN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>REAL_SOLO</t>
+          <t>DRY_APPR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Независимый риэлтор</t>
+          <t>Приёмка / пункт</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>200000</v>
+        <v>20</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>приёмщик:1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>REALTOR</t>
+          <t>DRYCLEAN</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>REAL_AGENCY</t>
+          <t>DRY_FULL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Агентство недвижимости</t>
+          <t>Химчистка с оборудованием</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>50</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>business_center</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>4500000</v>
+        <v>80</v>
+      </c>
+      <c r="E126" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>оператор:2|приёмщик:1|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NOTARY</t>
+          <t>LAUNDRY</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NOTARY_OFFICE</t>
+          <t>LAUNDRY_SELF</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Нотариальная контора</t>
+          <t>Прачечная самообслуживания</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>30</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>business_center</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>5500000</v>
+        <v>60</v>
+      </c>
+      <c r="E127" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>residential_complex,bc_standard,market</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>оператор:1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EVALUATION</t>
+          <t>LAUNDRY</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EVAL_SOLO</t>
+          <t>LAUNDRY_FULL</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Оценщик-самозанятый</t>
+          <t>Промышленная прачечная</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>400000</v>
+        <v>200</v>
+      </c>
+      <c r="E128" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>эконом</t>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>оператор:3|водитель:1|менеджер:1</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EVALUATION</t>
+          <t>COMPCLUB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EVAL_AGENCY</t>
+          <t>CC_SMALL</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Оценочная компания</t>
+          <t>Клуб 10-15 мест</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>30</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>business_center</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>3000000</v>
+        <v>80</v>
+      </c>
+      <c r="E129" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,mall_standard</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>администратор:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>COMPCLUB</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CC_LARGE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Киберарена 30+ мест</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>200</v>
+      </c>
+      <c r="E130" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>премиум</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>администратор:3|техник:1|менеджер:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>DRIVING</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DRIVE_SMALL</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Автошкола 2-3 машины</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>50</v>
+      </c>
+      <c r="E131" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>residential,bc_standard,city_center</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>инструктор:2|администратор:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>DRIVING</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DRIVE_FULL</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Автошкола 8+ машин</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>120</v>
+      </c>
+      <c r="E132" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>residential,city_center,suburb</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>инструктор:5|администратор:1|методист:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>HOTEL</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>HOTEL_HOSTEL</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Хостел 20 койко-мест</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>150</v>
+      </c>
+      <c r="E133" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>администратор:2|горничная:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PVZ</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PVZ_SMALL</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ПВЗ 15 м²</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>15</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>эконом</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,market</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>оператор:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PVZ</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PVZ_FULL</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ПВЗ 35 м²</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>35</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>residential,residential_complex,bc_standard</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>оператор:2</t>
         </is>
       </c>
     </row>

--- a/data/kz/08_niche_formats.xlsx
+++ b/data/kz/08_niche_formats.xlsx
@@ -471,6 +471,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -555,7 +556,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -680,7 +680,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -776,7 +775,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -805,7 +804,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -815,7 +813,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NAIL_SOLO</t>
+          <t>MANICURE_SOLO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -844,7 +842,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -854,7 +851,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -897,7 +894,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NAIL_SALON</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -969,7 +966,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1008,7 +1004,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1018,7 +1013,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BROW_CABINET</t>
+          <t>BROW_STANDARD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1090,7 +1085,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1129,7 +1123,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1139,7 +1132,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LASH_CABINET</t>
+          <t>LASH_STANDARD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,7 +1175,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SUGAR_HOME</t>
+          <t>SUGARING_HOME</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1211,7 +1204,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1221,7 +1213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SUGAR_SOLO</t>
+          <t>SUGARING_SOLO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1250,7 +1242,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1260,7 +1251,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SUGAR_CABINET</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1332,7 +1323,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1371,7 +1361,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1453,7 +1442,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1549,7 +1537,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DENTAL_1CH</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1592,7 +1580,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1750,7 +1738,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1803,7 +1790,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>REPAIR_POINT</t>
+          <t>REPAIR_PHONE_KIOSK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1846,7 +1833,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>REPAIR_STUDIO</t>
+          <t>REPAIR_PHONE_STANDARD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1918,7 +1905,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2387,7 +2373,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2985,7 +2970,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3067,7 +3051,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3636,7 +3619,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PHARM_SMALL</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3679,7 +3662,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PHARM_FULL</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3722,7 +3705,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GROC_KIOSK</t>
+          <t>GROCERY_SOLO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3765,7 +3748,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GROC_STANDARD</t>
+          <t>GROCERY_STANDARD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3808,7 +3791,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GROC_SUPER</t>
+          <t>GROCERY_PREMIUM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4095,7 +4078,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4306,7 +4288,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4388,7 +4369,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4642,7 +4622,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4724,7 +4703,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5064,7 +5042,6 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5404,7 +5381,6 @@
           <t>rent_in_salon</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5887,7 +5863,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PVZ_SMALL</t>
+          <t>PVZ_SOLO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5930,7 +5906,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PVZ_FULL</t>
+          <t>PVZ_STANDARD</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">

--- a/data/kz/08_niche_formats.xlsx
+++ b/data/kz/08_niche_formats.xlsx
@@ -787,7 +787,7 @@
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>350000</v>
+        <v>330000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/data/kz/08_niche_formats.xlsx
+++ b/data/kz/08_niche_formats.xlsx
@@ -471,7 +471,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -818,7 +817,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Мастер в чужом салоне</t>
+          <t>Аренда места в чужом салоне</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -856,7 +855,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Кабинет 1-2 мастера</t>
+          <t>Своя точка (студия)</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -877,12 +876,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>residential,residential_complex,mall_standard</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>мастер_маникюра:2</t>
+          <t>residential,residential_complex</t>
         </is>
       </c>
     </row>
@@ -899,7 +893,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Студия маникюра</t>
+          <t>Точка в ТЦ</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -920,12 +914,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>city_center,mall_premium,mall_standard</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>мастер_маникюра:4|администратор:1</t>
+          <t>mall_standard,mall_premium</t>
         </is>
       </c>
     </row>

--- a/data/kz/08_niche_formats.xlsx
+++ b/data/kz/08_niche_formats.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Своя точка (студия)</t>
+          <t>Свой кабинет</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Точка в ТЦ</t>
+          <t>Стойка в торговом центре</t>
         </is>
       </c>
       <c r="D16" t="n">
